--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time.report.json</t>
+  </si>
+  <si>
+    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>story-article</t>
+  </si>
+  <si>
+    <t>2026-05-17T13:46:58.193Z</t>
+  </si>
+  <si>
+    <t>5 ways AbbVie is working to deliver medicines in half the time | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time.html</t>
+  </si>
+  <si>
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes.report.json</t>
   </si>
   <si>
@@ -46,12 +70,6 @@
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>story-article</t>
-  </si>
-  <si>
     <t>2026-05-17T12:01:41.409Z</t>
   </si>
   <si>
@@ -59,6 +77,78 @@
   </si>
   <si>
     <t>https://www.abbvie.com/who-we-are/our-stories/can-unlocking-one-million-genomes.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/elevating-health-care-for-all.report.json</t>
+  </si>
+  <si>
+    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/elevating-health-care-for-all</t>
+  </si>
+  <si>
+    <t>2026-05-17T13:47:05.143Z</t>
+  </si>
+  <si>
+    <t>Elevating health care for all | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/elevating-health-care-for-all.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick.report.json</t>
+  </si>
+  <si>
+    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick</t>
+  </si>
+  <si>
+    <t>2026-05-17T13:47:12.771Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Jonathon Sedgwick | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-jonathon-sedgwick.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","custom-image","custom-image","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability</t>
+  </si>
+  <si>
+    <t>2026-05-17T13:47:20.183Z</t>
+  </si>
+  <si>
+    <t>Starting with a spark: An inside look at environmental sustainability | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing</t>
+  </si>
+  <si>
+    <t>2026-05-17T13:47:28.484Z</t>
+  </si>
+  <si>
+    <t>The blueprint of you: Unlocking the potential of whole genome sequencing | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing.html</t>
   </si>
 </sst>
 </file>
@@ -447,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -508,6 +598,136 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -40,7 +40,7 @@
     <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time.report.json</t>
   </si>
   <si>
-    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time</t>
@@ -52,7 +52,7 @@
     <t>story-article</t>
   </si>
   <si>
-    <t>2026-05-17T13:46:58.193Z</t>
+    <t>2026-05-17T17:09:25.120Z</t>
   </si>
   <si>
     <t>5 ways AbbVie is working to deliver medicines in half the time | AbbVie</t>
@@ -64,13 +64,13 @@
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes.report.json</t>
   </si>
   <si>
-    <t>["hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes</t>
   </si>
   <si>
-    <t>2026-05-17T12:01:41.409Z</t>
+    <t>2026-05-18T05:31:00.505Z</t>
   </si>
   <si>
     <t>Can unlocking one million genomes help us discover medicines faster? | AbbVie</t>
@@ -82,13 +82,13 @@
     <t>who-we-are/our-stories/elevating-health-care-for-all.report.json</t>
   </si>
   <si>
-    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","custom-image","custom-image","quote","quote","quote","quote"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/elevating-health-care-for-all</t>
   </si>
   <si>
-    <t>2026-05-17T13:47:05.143Z</t>
+    <t>2026-05-17T17:09:32.147Z</t>
   </si>
   <si>
     <t>Elevating health care for all | AbbVie</t>
@@ -100,13 +100,13 @@
     <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick.report.json</t>
   </si>
   <si>
-    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","custom-image"]</t>
+    <t>["hero-container","hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","custom-image","quote","quote"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick</t>
   </si>
   <si>
-    <t>2026-05-17T13:47:12.771Z</t>
+    <t>2026-05-17T17:09:39.681Z</t>
   </si>
   <si>
     <t>Magnified featuring Jonathon Sedgwick | AbbVie</t>
@@ -118,13 +118,13 @@
     <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability.report.json</t>
   </si>
   <si>
-    <t>["cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","custom-image","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","custom-image","custom-image","custom-image"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability</t>
   </si>
   <si>
-    <t>2026-05-17T13:47:20.183Z</t>
+    <t>2026-05-17T17:09:47.692Z</t>
   </si>
   <si>
     <t>Starting with a spark: An inside look at environmental sustainability | AbbVie</t>
@@ -136,13 +136,13 @@
     <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing.report.json</t>
   </si>
   <si>
-    <t>["hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","hero-container","cta","story-card","story-card","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","custom-image","custom-image"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing</t>
   </si>
   <si>
-    <t>2026-05-17T13:47:28.484Z</t>
+    <t>2026-05-17T17:09:54.278Z</t>
   </si>
   <si>
     <t>The blueprint of you: Unlocking the potential of whole genome sequencing | AbbVie</t>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -52,7 +52,7 @@
     <t>story-article</t>
   </si>
   <si>
-    <t>2026-05-17T17:09:25.120Z</t>
+    <t>2026-05-18T08:21:28.803Z</t>
   </si>
   <si>
     <t>5 ways AbbVie is working to deliver medicines in half the time | AbbVie</t>
@@ -70,7 +70,7 @@
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes</t>
   </si>
   <si>
-    <t>2026-05-18T05:31:00.505Z</t>
+    <t>2026-05-18T08:18:55.716Z</t>
   </si>
   <si>
     <t>Can unlocking one million genomes help us discover medicines faster? | AbbVie</t>
@@ -88,7 +88,7 @@
     <t>who-we-are/our-stories/elevating-health-care-for-all</t>
   </si>
   <si>
-    <t>2026-05-17T17:09:32.147Z</t>
+    <t>2026-05-18T08:21:35.149Z</t>
   </si>
   <si>
     <t>Elevating health care for all | AbbVie</t>
@@ -106,7 +106,7 @@
     <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick</t>
   </si>
   <si>
-    <t>2026-05-17T17:09:39.681Z</t>
+    <t>2026-05-18T08:21:43.148Z</t>
   </si>
   <si>
     <t>Magnified featuring Jonathon Sedgwick | AbbVie</t>
@@ -124,7 +124,7 @@
     <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability</t>
   </si>
   <si>
-    <t>2026-05-17T17:09:47.692Z</t>
+    <t>2026-05-18T08:21:50.316Z</t>
   </si>
   <si>
     <t>Starting with a spark: An inside look at environmental sustainability | AbbVie</t>
@@ -142,7 +142,7 @@
     <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing</t>
   </si>
   <si>
-    <t>2026-05-17T17:09:54.278Z</t>
+    <t>2026-05-18T08:21:56.968Z</t>
   </si>
   <si>
     <t>The blueprint of you: Unlocking the potential of whole genome sequencing | AbbVie</t>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -52,7 +52,7 @@
     <t>story-article</t>
   </si>
   <si>
-    <t>2026-05-20T05:53:52.288Z</t>
+    <t>2026-05-20T11:48:04.614Z</t>
   </si>
   <si>
     <t>The math of migraine | AbbVie</t>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>who-we-are/our-stories/can-unlocking-one-million-genomes.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","carousel","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/can-unlocking-one-million-genomes</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>story-article</t>
+  </si>
+  <si>
+    <t>2026-05-20T15:17:55.351Z</t>
+  </si>
+  <si>
+    <t>Can unlocking one million genomes help us discover medicines faster? | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/can-unlocking-one-million-genomes.html</t>
+  </si>
+  <si>
     <t>who-we-are/our-stories/the-math-of-migraine.report.json</t>
   </si>
   <si>
@@ -44,12 +68,6 @@
   </si>
   <si>
     <t>who-we-are/our-stories/the-math-of-migraine</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>story-article</t>
   </si>
   <si>
     <t>2026-05-20T05:53:52.288Z</t>
@@ -447,15 +465,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -508,6 +524,32 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -52,7 +52,7 @@
     <t>story-article</t>
   </si>
   <si>
-    <t>2026-05-20T15:17:55.351Z</t>
+    <t>2026-05-20T15:54:58.749Z</t>
   </si>
   <si>
     <t>Can unlocking one million genomes help us discover medicines faster? | AbbVie</t>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>_reportFile</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>https://www.abbvie.com/who-we-are/our-stories/the-math-of-migraine.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","quote","quote","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie</t>
+  </si>
+  <si>
+    <t>2026-05-21T18:42:39.624Z</t>
+  </si>
+  <si>
+    <t>Three ways AI is changing drug discovery at AbbVie | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie.html</t>
   </si>
 </sst>
 </file>
@@ -465,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -552,6 +570,32 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -88,7 +88,7 @@
     <t>who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie</t>
   </si>
   <si>
-    <t>2026-05-21T18:42:39.624Z</t>
+    <t>2026-05-21T19:44:22.712Z</t>
   </si>
   <si>
     <t>Three ways AI is changing drug discovery at AbbVie | AbbVie</t>

--- a/tools/importer/reports/import-story-article.report.xlsx
+++ b/tools/importer/reports/import-story-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="705">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,22 +37,292 @@
     <t>url</t>
   </si>
   <si>
+    <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>story-article</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:18.472Z</t>
+  </si>
+  <si>
+    <t>5 ways AbbVie is working to deliver medicines in half the time | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/5-ways-abbvie-work-to-deliver-medicines-in-half-the-time.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-history-discovery-why-we-focus-on-eye-cares-toughest-diseases.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","accordion","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-history-discovery-why-we-focus-on-eye-cares-toughest-diseases</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:26.448Z</t>
+  </si>
+  <si>
+    <t>A history of discovery: Why we focus on challenging eye care diseases | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/a-history-discovery-why-we-focus-on-eye-cares-toughest-diseases.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-journey-of-sight-progress.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-journey-of-sight-progress</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:35.290Z</t>
+  </si>
+  <si>
+    <t>A journey of sight: Progress toward treating neglected tropical diseases | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/a-journey-of-sight-progress.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-legacy-of-leadership-in-mental-health.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-legacy-of-leadership-in-mental-health</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:42.714Z</t>
+  </si>
+  <si>
+    <t>How AbbVie is working to push boundaries in mental health research | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/a-legacy-of-leadership-in-mental-health.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-molecular-behavior-chart-speeding-up-research-with-predictive-analytics.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/a-molecular-behavior-chart-speeding-up-research-with-predictive-analytics</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:50.632Z</t>
+  </si>
+  <si>
+    <t>A molecular behavior chart: speeding up research with predictive analytics | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/a-molecular-behavior-chart-speeding-up-research-with-predictive-analytics.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-rebuilds-north-chicagos-middle-school-inspiring-students-to-reach-higher.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-rebuilds-north-chicagos-middle-school-inspiring-students-to-reach-higher</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:08:59.683Z</t>
+  </si>
+  <si>
+    <t>AbbVie rebuilds North Chicago’s middle school, inspiring students to reach higher | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/abbvie-rebuilds-north-chicagos-middle-school-inspiring-students-to-reach-higher.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-research-collaborative.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-image","custom-title","text-container","text-container","text-container","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-research-collaborative</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:07.002Z</t>
+  </si>
+  <si>
+    <t>AbbVie Research Collaborative | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/abbvie-research-collaborative.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-volunteers-return-to-serving.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvie-volunteers-return-to-serving</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:14.132Z</t>
+  </si>
+  <si>
+    <t>AbbVie volunteers return to serving global communities through Week of Possibilities | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/abbvie-volunteers-return-to-serving.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvies-2024-working-parents-finding-purpose-in-adversity.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/abbvies-2024-working-parents-finding-purpose-in-adversity</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:21.582Z</t>
+  </si>
+  <si>
+    <t>AbbVies 2024 Working Parents Finding Purpose in Adversity | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/abbvies-2024-working-parents-finding-purpose-in-adversity.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/advancing-a-public-health-approach-to-patient-safety.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/advancing-a-public-health-approach-to-patient-safety</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:28.069Z</t>
+  </si>
+  <si>
+    <t>Advancing a public health approach to patient safety | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/advancing-a-public-health-approach-to-patient-safety.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/advice-from-scientist-turned-physician-turned-robot-builder-be-curious.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/advice-from-scientist-turned-physician-turned-robot-builder-be-curious</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:34.558Z</t>
+  </si>
+  <si>
+    <t>Advice from a scientist turned physician turned robot builder -- be curious | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/advice-from-scientist-turned-physician-turned-robot-builder-be-curious.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ambassadors-in-action.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","quote","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ambassadors-in-action</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:41.515Z</t>
+  </si>
+  <si>
+    <t>Ambassadors in action | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/ambassadors-in-action.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/an-innovative-approach-to-improve-maternal-health.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/an-innovative-approach-to-improve-maternal-health</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:09:48.270Z</t>
+  </si>
+  <si>
+    <t>An Innovative Approach to Improve Maternal Health | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/an-innovative-approach-to-improve-maternal-health.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/breaking-the-rules-of-science-to-treat-cancer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","accordion","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/breaking-the-rules-of-science-to-treat-cancer</t>
+  </si>
+  <si>
+    <t>2026-05-27T19:49:27.465Z</t>
+  </si>
+  <si>
+    <t>Breaking the rules of science to treat cancer | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/breaking-the-rules-of-science-to-treat-cancer.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/btk-protein-good-bad-and-ugly.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/btk-protein-good-bad-and-ugly</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:04.049Z</t>
+  </si>
+  <si>
+    <t>BTK protein: the good, the bad and the ugly | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/btk-protein-good-bad-and-ugly.html</t>
+  </si>
+  <si>
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes.report.json</t>
   </si>
   <si>
-    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","carousel","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image"]</t>
+    <t>["hero-container","hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","carousel"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/can-unlocking-one-million-genomes</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>story-article</t>
-  </si>
-  <si>
-    <t>2026-05-20T15:54:58.749Z</t>
+    <t>2026-05-27T16:10:10.589Z</t>
   </si>
   <si>
     <t>Can unlocking one million genomes help us discover medicines faster? | AbbVie</t>
@@ -61,16 +331,1456 @@
     <t>https://www.abbvie.com/who-we-are/our-stories/can-unlocking-one-million-genomes.html</t>
   </si>
   <si>
+    <t>who-we-are/our-stories/can-we-find-cures-faster.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/can-we-find-cures-faster</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:18.525Z</t>
+  </si>
+  <si>
+    <t>Can we find cures faster? | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/can-we-find-cures-faster.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/celebrating-abbvies-2025-working-parents-caregivers.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/celebrating-abbvies-2025-working-parents-caregivers</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:27.054Z</t>
+  </si>
+  <si>
+    <t>Celebrating AbbVies Working Parents Caregivers | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/celebrating-abbvies-2025-working-parents-caregivers.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/change-from-within.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/change-from-within</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:34.248Z</t>
+  </si>
+  <si>
+    <t>Change from within: Kenyan mom groups help families and communities thrive | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/change-from-within.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/chasing-the-value-of-a-walk-down-the-aisle.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/chasing-the-value-of-a-walk-down-the-aisle</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:41.622Z</t>
+  </si>
+  <si>
+    <t>Chasing the value of a walk down the aisle | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/chasing-the-value-of-a-walk-down-the-aisle.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/chembeads-improving-artificial-intelligence-through-human-ingenuity.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/chembeads-improving-artificial-intelligence-through-human-ingenuity</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:49.250Z</t>
+  </si>
+  <si>
+    <t>ChemBeads: improving artificial intelligence through human ingenuity | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/chembeads-improving-artificial-intelligence-through-human-ingenuity.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/childhood-cancer-patients-and-their-families-find-a-home-away-from-home.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/childhood-cancer-patients-and-their-families-find-a-home-away-from-home</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:10:57.206Z</t>
+  </si>
+  <si>
+    <t>Childhood cancer patients and their families find a home away from home | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/childhood-cancer-patients-and-their-families-find-a-home-away-from-home.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/connecting-patients-with-care-3-lessons-learned-during-covid-19.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","accordion"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/connecting-patients-with-care-3-lessons-learned-during-covid-19</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:03.931Z</t>
+  </si>
+  <si>
+    <t>Connecting patients with care: 3 lessons learned during COVID-19 | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/connecting-patients-with-care-3-lessons-learned-during-covid-19.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-government-affairs-director-educates-and-empowers.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-government-affairs-director-educates-and-empowers</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:12.321Z</t>
+  </si>
+  <si>
+    <t>Day in the Life: Government affairs director educates and empowers | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/day-in-life-government-affairs-director-educates-and-empowers.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-meet-director-clearing-path-for-patient-access.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","carousel","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-meet-director-clearing-path-for-patient-access</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:19.888Z</t>
+  </si>
+  <si>
+    <t>Day in the Life: Meet a Director Clearing the Path for Patient Access | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/day-in-life-meet-director-clearing-path-for-patient-access.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-meet-engineer-promoting-diversity-within-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-life-meet-engineer-promoting-diversity-within-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:28.608Z</t>
+  </si>
+  <si>
+    <t>Day in the Life: Meet an engineer fostering diversity and inclusion within manufacturing | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/day-in-life-meet-engineer-promoting-diversity-within-manufacturing.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-the-life-creating-impact-with-nonprofit-partners.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/day-in-the-life-creating-impact-with-nonprofit-partners</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:36.044Z</t>
+  </si>
+  <si>
+    <t>Day in the Life: Creating impact with nonprofit partners | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/day-in-the-life-creating-impact-with-nonprofit-partners.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/decoding-immune-systems-secrets-inside-the-discovery-of-a-new-medicine.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/decoding-immune-systems-secrets-inside-the-discovery-of-a-new-medicine</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:42.940Z</t>
+  </si>
+  <si>
+    <t>Decoding the immune system’s secrets: inside the discovery of a new medicine | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/decoding-immune-systems-secrets-inside-the-discovery-of-a-new-medicine.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/digital-science-lab.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-image","custom-title","text-container","text-container","text-container","accordion","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/digital-science-lab</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:50.386Z</t>
+  </si>
+  <si>
+    <t>Digital Science Lab | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/digital-science-lab.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/discovery-files-vision-for-blood-cancer-patients.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","accordion","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/discovery-files-vision-for-blood-cancer-patients</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:11:57.802Z</t>
+  </si>
+  <si>
+    <t>Discovery Files: A Vision for Blood Cancer Patients | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/discovery-files-vision-for-blood-cancer-patients.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/elevating-health-care-for-all.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/elevating-health-care-for-all</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:05.065Z</t>
+  </si>
+  <si>
+    <t>Elevating health care for all | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/elevating-health-care-for-all.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/empowering-innovation-through-the-abbvie-foundation-health-equit.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/empowering-innovation-through-the-abbvie-foundation-health-equit</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:12.086Z</t>
+  </si>
+  <si>
+    <t>Empowering Innovation Through the AbbVie Foundation Health Equity Accelerator | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/empowering-innovation-through-the-abbvie-foundation-health-equit.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ensuring-patients-around-world-get-medicines-during-covid-19.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ensuring-patients-around-world-get-medicines-during-covid-19</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:19.045Z</t>
+  </si>
+  <si>
+    <t>Ensuring patients around the world get medicines during COVID-19 | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/ensuring-patients-around-world-get-medicines-during-covid-19.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/everyones-talking-about-data-science.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/everyones-talking-about-data-science</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:25.933Z</t>
+  </si>
+  <si>
+    <t>Everyone’s talking about data science and analytics. Here’s how AbbVie approaches it. | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/everyones-talking-about-data-science.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/expert-insights-the-promise-of-genetic-medicine-and-abbvies-role-in-research.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","carousel","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/expert-insights-the-promise-of-genetic-medicine-and-abbvies-role-in-research</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:33.274Z</t>
+  </si>
+  <si>
+    <t>Genetic Medicine and AbbVie’s Role in Research | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/expert-insights-the-promise-of-genetic-medicine-and-abbvies-role-in-research.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/finding-hope-in-a-pandemic-a-conversation-with-two-hepatitis-c.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","quote","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/finding-hope-in-a-pandemic-a-conversation-with-two-hepatitis-c</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:02.356Z</t>
+  </si>
+  <si>
+    <t>Finding hope in a pandemic: A conversation with two hepatitis C experts | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/finding-hope-in-a-pandemic--a-conversation-with-two-hepatitis-c-.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/five-reasons-why-small-cell-lung-cancer-is-tough-to-treat.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","carousel","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/five-reasons-why-small-cell-lung-cancer-is-tough-to-treat</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:47.829Z</t>
+  </si>
+  <si>
+    <t>Five reasons why small cell lung cancer is tough to treat | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/five-reasons-why-small-cell-lung-cancer-is-tough-to-treat.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/five-technologies-supporting-progress-in-challenging-diseases.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/five-technologies-supporting-progress-in-challenging-diseases</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:12:54.420Z</t>
+  </si>
+  <si>
+    <t>Five Technologies Supporting Progress in Challenging Diseases | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/five-technologies-supporting-progress-in-challenging-diseases.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/going-inside-prison-walls-to-help-eliminate-hepatitis-c.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/going-inside-prison-walls-to-help-eliminate-hepatitis-c</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:03.012Z</t>
+  </si>
+  <si>
+    <t>Going inside prison walls to help eliminate hepatitis C | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/going-inside-prison-walls-to-help-eliminate-hepatitis-c.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/green-chemistry-cleaner-faster-chemical-reactions.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","carousel","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/green-chemistry-cleaner-faster-chemical-reactions</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:10.509Z</t>
+  </si>
+  <si>
+    <t>Green chemistry: cleaner, faster chemical reactions | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/green-chemistry-cleaner-faster-chemical-reactions.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/growing-sustainably-through-innovation-how-abbvie-takes-action.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/growing-sustainably-through-innovation-how-abbvie-takes-action</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:17.568Z</t>
+  </si>
+  <si>
+    <t>Growing sustainably through innovation: How AbbVie takes action | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/growing-sustainably-through-innovation-how-abbvie-takes-action.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/hepatitis-c-mysterious-virus-that-met-its-match.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/hepatitis-c-mysterious-virus-that-met-its-match</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:26.253Z</t>
+  </si>
+  <si>
+    <t>Hepatitis C: the mysterious virus that met its match | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/hepatitis-c-mysterious-virus-that-met-its-match.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-abbvie-is-bringing-antiviral-expertise-to-covid-19-battle.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-abbvie-is-bringing-antiviral-expertise-to-covid-19-battle</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:33.642Z</t>
+  </si>
+  <si>
+    <t>How AbbVie is bringing antiviral expertise to the COVID-19 battle | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-abbvie-is-bringing-antiviral-expertise-to-covid-19-battle.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-abbvies-integrated-operations-help-prevent-drug-shortages.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-abbvies-integrated-operations-help-prevent-drug-shortages</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:42.636Z</t>
+  </si>
+  <si>
+    <t>AbbVie’s Resilient Global Distribution Network Helps Prevent Drug Shortages | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-abbvies-integrated-operations-help-prevent-drug-shortages.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-employee-resource-groups-create-meaningful-impact-at-abbvie.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-employee-resource-groups-create-meaningful-impact-at-abbvie</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:51.043Z</t>
+  </si>
+  <si>
+    <t>Employee Resource Groups Drive Inclusion and Change at AbbVie | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-employee-resource-groups-create-meaningful-impact-at-abbvie.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-medicinal-chemists-are-creating-new-weapons-against-autoimmune-diseases.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","quote","quote","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-medicinal-chemists-are-creating-new-weapons-against-autoimmune-diseases</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:13:59.406Z</t>
+  </si>
+  <si>
+    <t>How medicinal chemists are creating new weapons against autoimmune diseases | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-medicinal-chemists-are-creating-new-weapons-against-autoimmune-diseases.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-patient-voices-are-changing-medicine.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-patient-voices-are-changing-medicine</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:06.813Z</t>
+  </si>
+  <si>
+    <t>How patient voices are changing medicine | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-patient-voices-are-changing-medicine.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-the-parkinsons-disease-community-is-shaping-the-future.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-the-parkinsons-disease-community-is-shaping-the-future</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:12.926Z</t>
+  </si>
+  <si>
+    <t>How the Parkinson’s Disease Community and AbbVie are Shaping the Future of Care | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-the-parkinsons-disease-community-is-shaping-the-future.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-uterine-fibroids-feel-to-patient-who-is-also-doctor.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","accordion"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/how-uterine-fibroids-feel-to-patient-who-is-also-doctor</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:20.030Z</t>
+  </si>
+  <si>
+    <t>How uterine fibroids feel to a patient…who’s also a doctor | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/how-uterine-fibroids-feel-to-patient-who-is-also-doctor.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/immunologys-next-frontier.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","accordion","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/immunologys-next-frontier</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:28.061Z</t>
+  </si>
+  <si>
+    <t>Immunology’s Next Frontier  | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/immunologys-next-frontier.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/injecting-hope-one-vaccine-at-a-time.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/injecting-hope-one-vaccine-at-a-time</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:34.320Z</t>
+  </si>
+  <si>
+    <t>Injecting hope, one vaccine at a time | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/injecting-hope-one-vaccine-at-a-time.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/inside-dream-initiative.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/inside-dream-initiative</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:42.387Z</t>
+  </si>
+  <si>
+    <t>Inside The DREAM Initiative | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/inside-dream-initiative.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/lessons-from-a-lifelong-journey-with-psoriasis.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","accordion","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/lessons-from-a-lifelong-journey-with-psoriasis</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:49.534Z</t>
+  </si>
+  <si>
+    <t>Lessons from a lifelong journey with psoriasis | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/lessons-from-a-lifelong-journey-with-psoriasis.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/life-after-stroke-living-with-and-researching-spasticity.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","carousel","accordion"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/life-after-stroke-living-with-and-researching-spasticity</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:14:57.428Z</t>
+  </si>
+  <si>
+    <t>Life after stroke: Living with and researching spasticity | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/life-after-stroke-living-with-and-researching-spasticity.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/little-patients-big-impact.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/little-patients-big-impact</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:04.647Z</t>
+  </si>
+  <si>
+    <t>Little patients, big impact: Our approach to pediatric oncology | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/little-patients-big-impact.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/living-with-an-illness.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/living-with-an-illness</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:12.014Z</t>
+  </si>
+  <si>
+    <t>How AbbVie makes medications more accessible | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/living-with-an-illness.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/living-with-unknowns-alzheimers-disease.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/living-with-unknowns-alzheimers-disease</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:18.827Z</t>
+  </si>
+  <si>
+    <t>Living with the unknowns of Alzheimer’s disease | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/living-with-unknowns-alzheimers-disease.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-darin-messina.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-darin-messina</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:26.627Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Darin Messina | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-darin-messina.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-edrice-simmons.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-edrice-simmons</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:34.413Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Edrice Simmons | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-edrice-simmons.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-johanna-corbin.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","quote","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-johanna-corbin</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:42.989Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Johanna Corbin | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-johanna-corbin.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-jonathon-sedgwick</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:49.573Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Jonathon Sedgwick | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-jonathon-sedgwick.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-linda-scarazzini.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-linda-scarazzini</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:15:57.349Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Linda Scarazzini | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-linda-scarazzini.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-matt-widman.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-matt-widman</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:05.002Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Matt Widman | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-matt-widman.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-nicholas-donoghoe.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-nicholas-donoghoe</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:13.219Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Nicholas Donoghoe | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-nicholas-donoghoe.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-sean-mcewen.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-sean-mcewen</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:20.213Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Sean McEwen | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-sean-mcewen.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-shuhong-zhang.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/magnified-featuring-shuhong-zhang</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:27.438Z</t>
+  </si>
+  <si>
+    <t>Magnified featuring Shuhong Zhang | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/magnified-featuring-shuhong-zhang.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/make-complicated-simple-inside-world-human-factors-engineers.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/make-complicated-simple-inside-world-human-factors-engineers</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:36.524Z</t>
+  </si>
+  <si>
+    <t>Make the complicated simple: Inside the world of Human Factors Engineers | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/make-complicated-simple-inside-world-human-factors-engineers.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/making-it-migraine-friendly-why-were-reimagining-workplace.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","accordion","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/making-it-migraine-friendly-why-were-reimagining-workplace</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:42.942Z</t>
+  </si>
+  <si>
+    <t>Making it migraine-friendly: Why we’re reimagining the workplace | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/making-it-migraine-friendly-why-were-reimagining-workplace.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/meet-the-arch-a-time-saving-tool-for-researchers-focused-on-finding-cures.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/meet-the-arch-a-time-saving-tool-for-researchers-focused-on-finding-cures</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:50.534Z</t>
+  </si>
+  <si>
+    <t>Meet the ARCH, a time-saving tool for researchers focused on finding cures | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/meet-the-arch-a-time-saving-tool-for-researchers-focused-on-finding-cures.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/more-than-a-stiff-neck-the-impact-of-living-with-cervical-dyston.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/more-than-a-stiff-neck-the-impact-of-living-with-cervical-dyston</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:16:58.266Z</t>
+  </si>
+  <si>
+    <t>More than a stiff neck: the impact of living with cervical dystonia | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/more-than-a-stiff-neck-the-impact-of-living-with-cervical-dyston.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/more-than-skin-deep-3-lessons-for-expanding-equity-in-dermatology.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/more-than-skin-deep-3-lessons-for-expanding-equity-in-dermatology</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:17:06.501Z</t>
+  </si>
+  <si>
+    <t>More than Skin Deep: 3 Lessons for Expanding Equity in Dermatology | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/more-than-skin-deep-3-lessons-for-expanding-equity-in-dermatology.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/much-more-than-itchy-skin-breaking-down-complexities-atopic-dermatitis.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","accordion"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/much-more-than-itchy-skin-breaking-down-complexities-atopic-dermatitis</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:17:14.107Z</t>
+  </si>
+  <si>
+    <t>More than itchy skin | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/much-more-than-itchy-skin-breaking-down-complexities-atopic-dermatitis.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/navigating-the-hidden-side-of-cancer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/navigating-the-hidden-side-of-cancer</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:17:23.369Z</t>
+  </si>
+  <si>
+    <t>Navigating the hidden side of cancer | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/navigating-the-hidden-side-of-cancer.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/navigating-ulcerative-colitis-as-a-child.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/navigating-ulcerative-colitis-as-a-child</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:09.481Z</t>
+  </si>
+  <si>
+    <t>Navigating ulcerative colitis as a child | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/navigating-ulcerative-colitis-as-a-child.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/new-microsite-clinic-brings-healthcare-to-chicago-southwest-side.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/new-microsite-clinic-brings-healthcare-to-chicago-southwest-side</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:16.908Z</t>
+  </si>
+  <si>
+    <t>AbbVie Foundation Supports New Chicago Healthcare Clinic for Underserved Communities | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/new-microsite-clinic-brings-healthcare-to-chicago-southwest-side.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/not-good-enough-behind-the-drive-to-give-cancer-patients-more-time.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/not-good-enough-behind-the-drive-to-give-cancer-patients-more-time</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:24.868Z</t>
+  </si>
+  <si>
+    <t>Not good enough: behind the drive to give cancer patients more time | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/not-good-enough-behind-the-drive-to-give-cancer-patients-more-time.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/one-veterans-journey-and-abbvies-commitment-to-mental-health-research.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/one-veterans-journey-and-abbvies-commitment-to-mental-health-research</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:31.173Z</t>
+  </si>
+  <si>
+    <t>One Veteran's Journey with Depression and AbbVie's Commitment to Mental Health Research | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/one-veterans-journey-and-abbvies-commitment-to-mental-health-research.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/precision-medicine-its-not-just-for-oncology-anymore.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/precision-medicine-its-not-just-for-oncology-anymore</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:39.348Z</t>
+  </si>
+  <si>
+    <t>Precision Medicine – it’s not just for oncology anymore | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/precision-medicine-its-not-just-for-oncology-anymore.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/putting-our-people-first-abbvies-family-benefits.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","carousel","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/putting-our-people-first-abbvies-family-benefits</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:46.616Z</t>
+  </si>
+  <si>
+    <t>Putting our people first AbbVie’s family benefits | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/putting-our-people-first-abbvies-family-benefits.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ready-set-launch-abbvie-opens-new-facility-in-the-bay-area.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","carousel","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/ready-set-launch-abbvie-opens-new-facility-in-the-bay-area</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:19:53.378Z</t>
+  </si>
+  <si>
+    <t>Ready, set, launch: AbbVie opens new facility in the Bay Area | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/ready-set-launch-abbvie-opens-new-facility-in-the-bay-area.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-people-real-inspiration-joes-story.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","custom-title","custom-title","text-container","text-container","text-container","text-container","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-people-real-inspiration-joes-story</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:01.746Z</t>
+  </si>
+  <si>
+    <t>Real People, Real Inspiration: Joe’s Story | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/real-people-real-inspiration-joes-story.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-world-data-rounds-out-value-picture-drugs.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-world-data-rounds-out-value-picture-drugs</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:08.700Z</t>
+  </si>
+  <si>
+    <t>Real-world data rounds out value picture of drugs | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/real-world-data-rounds-out-value-picture-drugs.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-world-evidence-uncovers-gaps-in-ibd-care.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/real-world-evidence-uncovers-gaps-in-ibd-care</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:17.415Z</t>
+  </si>
+  <si>
+    <t>Real-World Evidence in IBD: Driving Innovative Approaches to Care | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/real-world-evidence-uncovers-gaps-in-IBD-care.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/rebuilding-puerto-rico-one-community-health-center-at-a-time.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/rebuilding-puerto-rico-one-community-health-center-at-a-time</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:24.352Z</t>
+  </si>
+  <si>
+    <t>Rebuilding Puerto Rico, one community health center at a time | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/rebuilding-puerto-rico-one-community-health-center-at-a-time.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/recognizing-the-mental-health-impact-of-chronic-skin-disease.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/recognizing-the-mental-health-impact-of-chronic-skin-disease</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:31.641Z</t>
+  </si>
+  <si>
+    <t>Recognizing the mental health impact of chronic skin disease | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/recognizing-the-mental-health-impact-of-chronic-skin-disease.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/resilient-reality-the-emotional-toll-of-ovarian-cancer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/resilient-reality-the-emotional-toll-of-ovarian-cancer</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:40.997Z</t>
+  </si>
+  <si>
+    <t>Resilient Reality: The Emotional Toll of Ovarian Cancer | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/resilient-reality-the-emotional-toll-of-ovarian-cancer.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/sharpening-focus-on-eye-diseases-caused-by-diabetes.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/sharpening-focus-on-eye-diseases-caused-by-diabetes</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:48.413Z</t>
+  </si>
+  <si>
+    <t>Sharpening focus on eye diseases caused by diabetes | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/sharpening-focus-on-eye-diseases-caused-by-diabetes.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/shedding-light-upon-a-misunderstood-skin-condition-hidradenitis.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","accordion"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/shedding-light-upon-a-misunderstood-skin-condition-hidradenitis</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:20:56.010Z</t>
+  </si>
+  <si>
+    <t>Shedding light upon a misunderstood skin condition: Hidradenitis Suppurativa | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/shedding-light-upon-a-misunderstood-skin-condition-hidradenitis.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/shining-light-on-glaucoma-and-eye-health.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","carousel","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/shining-light-on-glaucoma-and-eye-health</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:02.871Z</t>
+  </si>
+  <si>
+    <t>Shining a light on glaucoma and eye health | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/shining-light-on-glaucoma-and-eye-health.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/specialized-research-in-chaotic-systems-sparcs.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-image","custom-title","text-container","text-container","text-container","accordion","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/specialized-research-in-chaotic-systems-sparcs</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:10.819Z</t>
+  </si>
+  <si>
+    <t>Specialized Research in Chaotic Systems (SPaRCS) | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/specialized-research-in-chaotic-systems-sparcs.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:18.525Z</t>
+  </si>
+  <si>
+    <t>Starting with a spark: An inside look at environmental sustainability | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/starting-with-a-spark-an-inside-look-at-environmental-sustainability.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/striving-for-patient-centricity-down-to-the-packaging.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/striving-for-patient-centricity-down-to-the-packaging</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:25.387Z</t>
+  </si>
+  <si>
+    <t>Striving for patient centricity, down to the packaging | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/striving-for-patient-centricity-down-to-the-packaging.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/stronger-together-convergence-minds-and-data.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/stronger-together-convergence-minds-and-data</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:31.607Z</t>
+  </si>
+  <si>
+    <t>Stronger together: A convergence of minds and data | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/stronger-together-convergence-minds-and-data.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/synthetic-control-arm-end-placebos.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/synthetic-control-arm-end-placebos</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:38.366Z</t>
+  </si>
+  <si>
+    <t>Synthetic control arm: the end of placebos? | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/synthetic-control-arm-end-placebos.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:45.792Z</t>
+  </si>
+  <si>
+    <t>The blueprint of you: Unlocking the potential of whole genome sequencing | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-blueprint-of-you-unlocking-potential-whole-genome-sequencing.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-hardest-hit-how-nonprofits-rise-to-challenge-covid-19.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-hardest-hit-how-nonprofits-rise-to-challenge-covid-19</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:52.157Z</t>
+  </si>
+  <si>
+    <t>The hardest-hit: How nonprofits rise to the challenge of COVID-19 | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-hardest-hit-how-nonprofits-rise-to-challenge-covid-19.html</t>
+  </si>
+  <si>
     <t>who-we-are/our-stories/the-math-of-migraine.report.json</t>
   </si>
   <si>
-    <t>["hero-container","cta","story-card","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","carousel","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","accordion"]</t>
+    <t>["hero-container","hero-container","cta","story-card","accordion","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","carousel"]</t>
   </si>
   <si>
     <t>who-we-are/our-stories/the-math-of-migraine</t>
   </si>
   <si>
-    <t>2026-05-20T05:53:52.288Z</t>
+    <t>2026-05-27T19:32:41.860Z</t>
   </si>
   <si>
     <t>The math of migraine | AbbVie</t>
@@ -79,6 +1789,132 @@
     <t>https://www.abbvie.com/who-we-are/our-stories/the-math-of-migraine.html</t>
   </si>
   <si>
+    <t>who-we-are/our-stories/the-persistence-lab-podcasts.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","hero-container","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-persistence-lab-podcasts</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:21:59.744Z</t>
+  </si>
+  <si>
+    <t>Podcasts | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-persistence-lab-podcasts.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-power-love-in-ibd.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","separator","separator","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-power-love-in-ibd</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:08.945Z</t>
+  </si>
+  <si>
+    <t>The power of love in IBD | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-power-love-in-ibd.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-story-behind-our-50-billion-rd-investment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-story-behind-our-50-billion-rd-investment</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:16.063Z</t>
+  </si>
+  <si>
+    <t>The story behind our $50 billion R&amp;D investment | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-story-behind-our-50-billion-rd-investment.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-value-of-education-from-a-dim-reality-to-a-bright-future.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","carousel","quote","quote","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/the-value-of-education-from-a-dim-reality-to-a-bright-future</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:24.056Z</t>
+  </si>
+  <si>
+    <t>The value of education: From a dim reality to a bright future | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/the-value-of-education-from-a-dim-reality-to-a-bright-future.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/then-and-now-renaissance-in-blood-cancer-treatment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","carousel","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/then-and-now-renaissance-in-blood-cancer-treatment</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:31.888Z</t>
+  </si>
+  <si>
+    <t>Then and now: A renaissance in blood cancer treatment | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/then-and-now-renaissance-in-blood-cancer-treatment.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/they-wont-back-down.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","quote","quote","quote","quote","quote","brightcove-video","brightcove-video","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/they-wont-back-down</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:39.962Z</t>
+  </si>
+  <si>
+    <t>They won’t back down | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/they-wont-back-down.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/three-factors-that-drove-transformational-integration-abbvie-allergan.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/three-factors-that-drove-transformational-integration-abbvie-allergan</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:46.449Z</t>
+  </si>
+  <si>
+    <t>Three factors that drove the transformational integration of AbbVie, Allergan | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/three-factors-that-drove-transformational-integration-abbvie-allergan.html</t>
+  </si>
+  <si>
     <t>who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie.report.json</t>
   </si>
   <si>
@@ -88,13 +1924,208 @@
     <t>who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie</t>
   </si>
   <si>
-    <t>2026-05-21T19:44:22.712Z</t>
+    <t>2026-05-27T14:57:16.319Z</t>
   </si>
   <si>
     <t>Three ways AI is changing drug discovery at AbbVie | AbbVie</t>
   </si>
   <si>
     <t>https://www.abbvie.com/who-we-are/our-stories/three-ways-ai-is-changing-drug-discovery-at-abbvie.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/time-is-hours.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/time-is-hours</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:22:54.335Z</t>
+  </si>
+  <si>
+    <t>Time is Hours | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/time-is-hours.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/transforming-cancer-care-from-the-inside-out.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","story-card","story-card","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","quote","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/transforming-cancer-care-from-the-inside-out</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:02.341Z</t>
+  </si>
+  <si>
+    <t>How AbbVie Supports Employees Touched by Cancer | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/transforming-cancer-care-from-the-inside-out.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/trapped-in-your-own-skin.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","accordion","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/trapped-in-your-own-skin</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:09.732Z</t>
+  </si>
+  <si>
+    <t>Trapped in your own skin | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/trapped-in-your-own-skin.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/two-lives-converging-in-the-fight-against-parkinsons.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/two-lives-converging-in-the-fight-against-parkinsons</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:18.772Z</t>
+  </si>
+  <si>
+    <t>Two Lives Converge in the Fight Against Parkinson’s | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/two-lives-converging-in-the-fight-against-parkinsons.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/unlocking-the-next-level-of-protein-degradation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/unlocking-the-next-level-of-protein-degradation</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:26.870Z</t>
+  </si>
+  <si>
+    <t>Unlocking the next level of protein degradation | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/unlocking-the-next-level-of-protein-degradation.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/voices-abbvie-reflecting-on-decade-impact.report.json</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/voices-abbvie-reflecting-on-decade-impact</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:33.768Z</t>
+  </si>
+  <si>
+    <t>Voices of AbbVie: Reflecting on a decade of impact | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/voices-abbvie-reflecting-on-decade-impact.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/what-does-it-take-to-discover-a-new-medicine.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","quote","brightcove-video","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/what-does-it-take-to-discover-a-new-medicine</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:42.032Z</t>
+  </si>
+  <si>
+    <t>What does it take to discover a new medicine? | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/what-does-it-take-to-discover-a-new-medicine.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-delivering-science-based-targets-are-key-to-sustainable-grow.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","carousel"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-delivering-science-based-targets-are-key-to-sustainable-grow</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:49.337Z</t>
+  </si>
+  <si>
+    <t>Why delivering science-based targets are key to sustainable growth | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/why-delivering-science-based-targets-are-key-to-sustainable-grow.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-isnt-medicine-one-size-fits-all.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","accordion","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-isnt-medicine-one-size-fits-all</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:23:57.466Z</t>
+  </si>
+  <si>
+    <t>Why isn’t medicine one size fits all? | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/why-isnt-medicine-one-size-fits-all.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-you-cant-wait-with-rheumatoid-arthritis.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","accordion","quote","brightcove-video"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/why-you-cant-wait-with-rheumatoid-arthritis</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:24:04.744Z</t>
+  </si>
+  <si>
+    <t>Why you can’t wait with rheumatoid arthritis | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/why-you-cant-wait-with-rheumatoid-arthritis.html</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/working-parents-2023-finding-comfort-in-community.report.json</t>
+  </si>
+  <si>
+    <t>["hero-container","cta","story-card","story-card","custom-image","custom-image","custom-image","custom-image","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","custom-title","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","text-container","separator","separator","separator","separator","separator","separator","separator","quote","quote"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-stories/working-parents-2023-finding-comfort-in-community</t>
+  </si>
+  <si>
+    <t>2026-05-27T16:24:12.275Z</t>
+  </si>
+  <si>
+    <t>Working Parents 2023: Finding comfort in community | AbbVie</t>
+  </si>
+  <si>
+    <t>https://www.abbvie.com/who-we-are/our-stories/working-parents-2023-finding-comfort-in-community.html</t>
   </si>
 </sst>
 </file>
@@ -483,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -596,6 +2627,2944 @@
         <v>27</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" t="s">
+        <v>170</v>
+      </c>
+      <c r="H28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G30" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>193</v>
+      </c>
+      <c r="G32" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>199</v>
+      </c>
+      <c r="G33" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>205</v>
+      </c>
+      <c r="G34" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" t="s">
+        <v>212</v>
+      </c>
+      <c r="H35" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>223</v>
+      </c>
+      <c r="G37" t="s">
+        <v>224</v>
+      </c>
+      <c r="H37" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>226</v>
+      </c>
+      <c r="B38" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" t="s">
+        <v>230</v>
+      </c>
+      <c r="H38" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>235</v>
+      </c>
+      <c r="G39" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>241</v>
+      </c>
+      <c r="G40" t="s">
+        <v>242</v>
+      </c>
+      <c r="H40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>247</v>
+      </c>
+      <c r="G41" t="s">
+        <v>248</v>
+      </c>
+      <c r="H41" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>253</v>
+      </c>
+      <c r="G42" t="s">
+        <v>254</v>
+      </c>
+      <c r="H42" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" t="s">
+        <v>258</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>259</v>
+      </c>
+      <c r="G43" t="s">
+        <v>260</v>
+      </c>
+      <c r="H43" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" t="s">
+        <v>263</v>
+      </c>
+      <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>265</v>
+      </c>
+      <c r="G44" t="s">
+        <v>266</v>
+      </c>
+      <c r="H44" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>268</v>
+      </c>
+      <c r="B45" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>271</v>
+      </c>
+      <c r="G45" t="s">
+        <v>272</v>
+      </c>
+      <c r="H45" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" t="s">
+        <v>276</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>277</v>
+      </c>
+      <c r="G46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>283</v>
+      </c>
+      <c r="G47" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>286</v>
+      </c>
+      <c r="B48" t="s">
+        <v>287</v>
+      </c>
+      <c r="C48" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>289</v>
+      </c>
+      <c r="G48" t="s">
+        <v>290</v>
+      </c>
+      <c r="H48" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>292</v>
+      </c>
+      <c r="B49" t="s">
+        <v>293</v>
+      </c>
+      <c r="C49" t="s">
+        <v>294</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>295</v>
+      </c>
+      <c r="G49" t="s">
+        <v>296</v>
+      </c>
+      <c r="H49" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" t="s">
+        <v>299</v>
+      </c>
+      <c r="C50" t="s">
+        <v>300</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>301</v>
+      </c>
+      <c r="G50" t="s">
+        <v>302</v>
+      </c>
+      <c r="H50" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" t="s">
+        <v>305</v>
+      </c>
+      <c r="C51" t="s">
+        <v>306</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>307</v>
+      </c>
+      <c r="G51" t="s">
+        <v>308</v>
+      </c>
+      <c r="H51" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>310</v>
+      </c>
+      <c r="B52" t="s">
+        <v>311</v>
+      </c>
+      <c r="C52" t="s">
+        <v>312</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>313</v>
+      </c>
+      <c r="G52" t="s">
+        <v>314</v>
+      </c>
+      <c r="H52" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" t="s">
+        <v>317</v>
+      </c>
+      <c r="C53" t="s">
+        <v>318</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>319</v>
+      </c>
+      <c r="G53" t="s">
+        <v>320</v>
+      </c>
+      <c r="H53" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" t="s">
+        <v>324</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>325</v>
+      </c>
+      <c r="G54" t="s">
+        <v>326</v>
+      </c>
+      <c r="H54" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>328</v>
+      </c>
+      <c r="B55" t="s">
+        <v>329</v>
+      </c>
+      <c r="C55" t="s">
+        <v>330</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>331</v>
+      </c>
+      <c r="G55" t="s">
+        <v>332</v>
+      </c>
+      <c r="H55" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>334</v>
+      </c>
+      <c r="B56" t="s">
+        <v>335</v>
+      </c>
+      <c r="C56" t="s">
+        <v>336</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>337</v>
+      </c>
+      <c r="G56" t="s">
+        <v>338</v>
+      </c>
+      <c r="H56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" t="s">
+        <v>342</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>343</v>
+      </c>
+      <c r="G57" t="s">
+        <v>344</v>
+      </c>
+      <c r="H57" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>346</v>
+      </c>
+      <c r="B58" t="s">
+        <v>347</v>
+      </c>
+      <c r="C58" t="s">
+        <v>348</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>349</v>
+      </c>
+      <c r="G58" t="s">
+        <v>350</v>
+      </c>
+      <c r="H58" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" t="s">
+        <v>353</v>
+      </c>
+      <c r="C59" t="s">
+        <v>354</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>355</v>
+      </c>
+      <c r="G59" t="s">
+        <v>356</v>
+      </c>
+      <c r="H59" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>358</v>
+      </c>
+      <c r="B60" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s">
+        <v>360</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>361</v>
+      </c>
+      <c r="G60" t="s">
+        <v>362</v>
+      </c>
+      <c r="H60" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>364</v>
+      </c>
+      <c r="B61" t="s">
+        <v>365</v>
+      </c>
+      <c r="C61" t="s">
+        <v>366</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>367</v>
+      </c>
+      <c r="G61" t="s">
+        <v>368</v>
+      </c>
+      <c r="H61" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B62" t="s">
+        <v>371</v>
+      </c>
+      <c r="C62" t="s">
+        <v>372</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s">
+        <v>373</v>
+      </c>
+      <c r="G62" t="s">
+        <v>374</v>
+      </c>
+      <c r="H62" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>376</v>
+      </c>
+      <c r="B63" t="s">
+        <v>377</v>
+      </c>
+      <c r="C63" t="s">
+        <v>378</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>379</v>
+      </c>
+      <c r="G63" t="s">
+        <v>380</v>
+      </c>
+      <c r="H63" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>382</v>
+      </c>
+      <c r="B64" t="s">
+        <v>383</v>
+      </c>
+      <c r="C64" t="s">
+        <v>384</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>385</v>
+      </c>
+      <c r="G64" t="s">
+        <v>386</v>
+      </c>
+      <c r="H64" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>388</v>
+      </c>
+      <c r="B65" t="s">
+        <v>389</v>
+      </c>
+      <c r="C65" t="s">
+        <v>390</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>391</v>
+      </c>
+      <c r="G65" t="s">
+        <v>392</v>
+      </c>
+      <c r="H65" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" t="s">
+        <v>395</v>
+      </c>
+      <c r="C66" t="s">
+        <v>396</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>397</v>
+      </c>
+      <c r="G66" t="s">
+        <v>398</v>
+      </c>
+      <c r="H66" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>400</v>
+      </c>
+      <c r="B67" t="s">
+        <v>401</v>
+      </c>
+      <c r="C67" t="s">
+        <v>402</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>403</v>
+      </c>
+      <c r="G67" t="s">
+        <v>404</v>
+      </c>
+      <c r="H67" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>406</v>
+      </c>
+      <c r="B68" t="s">
+        <v>407</v>
+      </c>
+      <c r="C68" t="s">
+        <v>408</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>409</v>
+      </c>
+      <c r="G68" t="s">
+        <v>410</v>
+      </c>
+      <c r="H68" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" t="s">
+        <v>413</v>
+      </c>
+      <c r="C69" t="s">
+        <v>414</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>415</v>
+      </c>
+      <c r="G69" t="s">
+        <v>416</v>
+      </c>
+      <c r="H69" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" t="s">
+        <v>419</v>
+      </c>
+      <c r="C70" t="s">
+        <v>420</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>421</v>
+      </c>
+      <c r="G70" t="s">
+        <v>422</v>
+      </c>
+      <c r="H70" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>424</v>
+      </c>
+      <c r="B71" t="s">
+        <v>425</v>
+      </c>
+      <c r="C71" t="s">
+        <v>426</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>427</v>
+      </c>
+      <c r="G71" t="s">
+        <v>428</v>
+      </c>
+      <c r="H71" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>430</v>
+      </c>
+      <c r="B72" t="s">
+        <v>431</v>
+      </c>
+      <c r="C72" t="s">
+        <v>432</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>433</v>
+      </c>
+      <c r="G72" t="s">
+        <v>434</v>
+      </c>
+      <c r="H72" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>436</v>
+      </c>
+      <c r="B73" t="s">
+        <v>437</v>
+      </c>
+      <c r="C73" t="s">
+        <v>438</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>439</v>
+      </c>
+      <c r="G73" t="s">
+        <v>440</v>
+      </c>
+      <c r="H73" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>442</v>
+      </c>
+      <c r="B74" t="s">
+        <v>443</v>
+      </c>
+      <c r="C74" t="s">
+        <v>444</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>445</v>
+      </c>
+      <c r="G74" t="s">
+        <v>446</v>
+      </c>
+      <c r="H74" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>448</v>
+      </c>
+      <c r="B75" t="s">
+        <v>449</v>
+      </c>
+      <c r="C75" t="s">
+        <v>450</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>451</v>
+      </c>
+      <c r="G75" t="s">
+        <v>452</v>
+      </c>
+      <c r="H75" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>454</v>
+      </c>
+      <c r="B76" t="s">
+        <v>455</v>
+      </c>
+      <c r="C76" t="s">
+        <v>456</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>457</v>
+      </c>
+      <c r="G76" t="s">
+        <v>458</v>
+      </c>
+      <c r="H76" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>460</v>
+      </c>
+      <c r="B77" t="s">
+        <v>461</v>
+      </c>
+      <c r="C77" t="s">
+        <v>462</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>463</v>
+      </c>
+      <c r="G77" t="s">
+        <v>464</v>
+      </c>
+      <c r="H77" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>466</v>
+      </c>
+      <c r="B78" t="s">
+        <v>467</v>
+      </c>
+      <c r="C78" t="s">
+        <v>468</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
+        <v>469</v>
+      </c>
+      <c r="G78" t="s">
+        <v>470</v>
+      </c>
+      <c r="H78" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>472</v>
+      </c>
+      <c r="B79" t="s">
+        <v>473</v>
+      </c>
+      <c r="C79" t="s">
+        <v>474</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" t="s">
+        <v>475</v>
+      </c>
+      <c r="G79" t="s">
+        <v>476</v>
+      </c>
+      <c r="H79" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>478</v>
+      </c>
+      <c r="B80" t="s">
+        <v>479</v>
+      </c>
+      <c r="C80" t="s">
+        <v>480</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" t="s">
+        <v>481</v>
+      </c>
+      <c r="G80" t="s">
+        <v>482</v>
+      </c>
+      <c r="H80" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>484</v>
+      </c>
+      <c r="B81" t="s">
+        <v>485</v>
+      </c>
+      <c r="C81" t="s">
+        <v>486</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>487</v>
+      </c>
+      <c r="G81" t="s">
+        <v>488</v>
+      </c>
+      <c r="H81" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>490</v>
+      </c>
+      <c r="B82" t="s">
+        <v>491</v>
+      </c>
+      <c r="C82" t="s">
+        <v>492</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" t="s">
+        <v>493</v>
+      </c>
+      <c r="G82" t="s">
+        <v>494</v>
+      </c>
+      <c r="H82" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>496</v>
+      </c>
+      <c r="B83" t="s">
+        <v>497</v>
+      </c>
+      <c r="C83" t="s">
+        <v>498</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>499</v>
+      </c>
+      <c r="G83" t="s">
+        <v>500</v>
+      </c>
+      <c r="H83" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>502</v>
+      </c>
+      <c r="B84" t="s">
+        <v>503</v>
+      </c>
+      <c r="C84" t="s">
+        <v>504</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
+        <v>505</v>
+      </c>
+      <c r="G84" t="s">
+        <v>506</v>
+      </c>
+      <c r="H84" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>508</v>
+      </c>
+      <c r="B85" t="s">
+        <v>509</v>
+      </c>
+      <c r="C85" t="s">
+        <v>510</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" t="s">
+        <v>511</v>
+      </c>
+      <c r="G85" t="s">
+        <v>512</v>
+      </c>
+      <c r="H85" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>514</v>
+      </c>
+      <c r="B86" t="s">
+        <v>515</v>
+      </c>
+      <c r="C86" t="s">
+        <v>516</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" t="s">
+        <v>517</v>
+      </c>
+      <c r="G86" t="s">
+        <v>518</v>
+      </c>
+      <c r="H86" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>520</v>
+      </c>
+      <c r="B87" t="s">
+        <v>521</v>
+      </c>
+      <c r="C87" t="s">
+        <v>522</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" t="s">
+        <v>523</v>
+      </c>
+      <c r="G87" t="s">
+        <v>524</v>
+      </c>
+      <c r="H87" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>526</v>
+      </c>
+      <c r="B88" t="s">
+        <v>527</v>
+      </c>
+      <c r="C88" t="s">
+        <v>528</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" t="s">
+        <v>529</v>
+      </c>
+      <c r="G88" t="s">
+        <v>530</v>
+      </c>
+      <c r="H88" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>532</v>
+      </c>
+      <c r="B89" t="s">
+        <v>533</v>
+      </c>
+      <c r="C89" t="s">
+        <v>534</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" t="s">
+        <v>535</v>
+      </c>
+      <c r="G89" t="s">
+        <v>536</v>
+      </c>
+      <c r="H89" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>538</v>
+      </c>
+      <c r="B90" t="s">
+        <v>539</v>
+      </c>
+      <c r="C90" t="s">
+        <v>540</v>
+      </c>
+      <c r="D90" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" t="s">
+        <v>541</v>
+      </c>
+      <c r="G90" t="s">
+        <v>542</v>
+      </c>
+      <c r="H90" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>544</v>
+      </c>
+      <c r="B91" t="s">
+        <v>545</v>
+      </c>
+      <c r="C91" t="s">
+        <v>546</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" t="s">
+        <v>547</v>
+      </c>
+      <c r="G91" t="s">
+        <v>548</v>
+      </c>
+      <c r="H91" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>550</v>
+      </c>
+      <c r="B92" t="s">
+        <v>551</v>
+      </c>
+      <c r="C92" t="s">
+        <v>552</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" t="s">
+        <v>553</v>
+      </c>
+      <c r="G92" t="s">
+        <v>554</v>
+      </c>
+      <c r="H92" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>556</v>
+      </c>
+      <c r="B93" t="s">
+        <v>557</v>
+      </c>
+      <c r="C93" t="s">
+        <v>558</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" t="s">
+        <v>559</v>
+      </c>
+      <c r="G93" t="s">
+        <v>560</v>
+      </c>
+      <c r="H93" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>562</v>
+      </c>
+      <c r="B94" t="s">
+        <v>563</v>
+      </c>
+      <c r="C94" t="s">
+        <v>564</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" t="s">
+        <v>565</v>
+      </c>
+      <c r="G94" t="s">
+        <v>566</v>
+      </c>
+      <c r="H94" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>568</v>
+      </c>
+      <c r="B95" t="s">
+        <v>569</v>
+      </c>
+      <c r="C95" t="s">
+        <v>570</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" t="s">
+        <v>571</v>
+      </c>
+      <c r="G95" t="s">
+        <v>572</v>
+      </c>
+      <c r="H95" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>574</v>
+      </c>
+      <c r="B96" t="s">
+        <v>575</v>
+      </c>
+      <c r="C96" t="s">
+        <v>576</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" t="s">
+        <v>577</v>
+      </c>
+      <c r="G96" t="s">
+        <v>578</v>
+      </c>
+      <c r="H96" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>580</v>
+      </c>
+      <c r="B97" t="s">
+        <v>581</v>
+      </c>
+      <c r="C97" t="s">
+        <v>582</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s">
+        <v>583</v>
+      </c>
+      <c r="G97" t="s">
+        <v>584</v>
+      </c>
+      <c r="H97" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>586</v>
+      </c>
+      <c r="B98" t="s">
+        <v>587</v>
+      </c>
+      <c r="C98" t="s">
+        <v>588</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" t="s">
+        <v>589</v>
+      </c>
+      <c r="G98" t="s">
+        <v>590</v>
+      </c>
+      <c r="H98" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>592</v>
+      </c>
+      <c r="B99" t="s">
+        <v>593</v>
+      </c>
+      <c r="C99" t="s">
+        <v>594</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
+        <v>595</v>
+      </c>
+      <c r="G99" t="s">
+        <v>596</v>
+      </c>
+      <c r="H99" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>598</v>
+      </c>
+      <c r="B100" t="s">
+        <v>599</v>
+      </c>
+      <c r="C100" t="s">
+        <v>600</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" t="s">
+        <v>601</v>
+      </c>
+      <c r="G100" t="s">
+        <v>602</v>
+      </c>
+      <c r="H100" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>604</v>
+      </c>
+      <c r="B101" t="s">
+        <v>605</v>
+      </c>
+      <c r="C101" t="s">
+        <v>606</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s">
+        <v>607</v>
+      </c>
+      <c r="G101" t="s">
+        <v>608</v>
+      </c>
+      <c r="H101" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>610</v>
+      </c>
+      <c r="B102" t="s">
+        <v>611</v>
+      </c>
+      <c r="C102" t="s">
+        <v>612</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" t="s">
+        <v>613</v>
+      </c>
+      <c r="G102" t="s">
+        <v>614</v>
+      </c>
+      <c r="H102" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>616</v>
+      </c>
+      <c r="B103" t="s">
+        <v>617</v>
+      </c>
+      <c r="C103" t="s">
+        <v>618</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" t="s">
+        <v>619</v>
+      </c>
+      <c r="G103" t="s">
+        <v>620</v>
+      </c>
+      <c r="H103" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>622</v>
+      </c>
+      <c r="B104" t="s">
+        <v>623</v>
+      </c>
+      <c r="C104" t="s">
+        <v>624</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" t="s">
+        <v>625</v>
+      </c>
+      <c r="G104" t="s">
+        <v>626</v>
+      </c>
+      <c r="H104" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>628</v>
+      </c>
+      <c r="B105" t="s">
+        <v>629</v>
+      </c>
+      <c r="C105" t="s">
+        <v>630</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" t="s">
+        <v>631</v>
+      </c>
+      <c r="G105" t="s">
+        <v>632</v>
+      </c>
+      <c r="H105" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>634</v>
+      </c>
+      <c r="B106" t="s">
+        <v>635</v>
+      </c>
+      <c r="C106" t="s">
+        <v>636</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" t="s">
+        <v>637</v>
+      </c>
+      <c r="G106" t="s">
+        <v>638</v>
+      </c>
+      <c r="H106" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>640</v>
+      </c>
+      <c r="B107" t="s">
+        <v>641</v>
+      </c>
+      <c r="C107" t="s">
+        <v>642</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" t="s">
+        <v>643</v>
+      </c>
+      <c r="G107" t="s">
+        <v>644</v>
+      </c>
+      <c r="H107" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>646</v>
+      </c>
+      <c r="B108" t="s">
+        <v>647</v>
+      </c>
+      <c r="C108" t="s">
+        <v>648</v>
+      </c>
+      <c r="D108" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" t="s">
+        <v>649</v>
+      </c>
+      <c r="G108" t="s">
+        <v>650</v>
+      </c>
+      <c r="H108" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>652</v>
+      </c>
+      <c r="B109" t="s">
+        <v>653</v>
+      </c>
+      <c r="C109" t="s">
+        <v>654</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s">
+        <v>655</v>
+      </c>
+      <c r="G109" t="s">
+        <v>656</v>
+      </c>
+      <c r="H109" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>658</v>
+      </c>
+      <c r="B110" t="s">
+        <v>659</v>
+      </c>
+      <c r="C110" t="s">
+        <v>660</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" t="s">
+        <v>661</v>
+      </c>
+      <c r="G110" t="s">
+        <v>662</v>
+      </c>
+      <c r="H110" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>664</v>
+      </c>
+      <c r="B111" t="s">
+        <v>665</v>
+      </c>
+      <c r="C111" t="s">
+        <v>666</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" t="s">
+        <v>667</v>
+      </c>
+      <c r="G111" t="s">
+        <v>668</v>
+      </c>
+      <c r="H111" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>670</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>671</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" t="s">
+        <v>672</v>
+      </c>
+      <c r="G112" t="s">
+        <v>673</v>
+      </c>
+      <c r="H112" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>675</v>
+      </c>
+      <c r="B113" t="s">
+        <v>676</v>
+      </c>
+      <c r="C113" t="s">
+        <v>677</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" t="s">
+        <v>678</v>
+      </c>
+      <c r="G113" t="s">
+        <v>679</v>
+      </c>
+      <c r="H113" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>681</v>
+      </c>
+      <c r="B114" t="s">
+        <v>682</v>
+      </c>
+      <c r="C114" t="s">
+        <v>683</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
+        <v>684</v>
+      </c>
+      <c r="G114" t="s">
+        <v>685</v>
+      </c>
+      <c r="H114" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>687</v>
+      </c>
+      <c r="B115" t="s">
+        <v>688</v>
+      </c>
+      <c r="C115" t="s">
+        <v>689</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" t="s">
+        <v>690</v>
+      </c>
+      <c r="G115" t="s">
+        <v>691</v>
+      </c>
+      <c r="H115" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>693</v>
+      </c>
+      <c r="B116" t="s">
+        <v>694</v>
+      </c>
+      <c r="C116" t="s">
+        <v>695</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" t="s">
+        <v>696</v>
+      </c>
+      <c r="G116" t="s">
+        <v>697</v>
+      </c>
+      <c r="H116" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>699</v>
+      </c>
+      <c r="B117" t="s">
+        <v>700</v>
+      </c>
+      <c r="C117" t="s">
+        <v>701</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" t="s">
+        <v>702</v>
+      </c>
+      <c r="G117" t="s">
+        <v>703</v>
+      </c>
+      <c r="H117" t="s">
+        <v>704</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
